--- a/marketing_surveys/001_powdered_juice_consumption_survey--marketing_surveys.xlsx
+++ b/marketing_surveys/001_powdered_juice_consumption_survey--marketing_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -792,8 +792,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -821,12 +821,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'18-24'}</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': '18-24'}</t>
+          <t>18-24</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'25-34'}</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '25-34'}</t>
+          <t>25-34</t>
         </is>
       </c>
     </row>
@@ -855,12 +855,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'35-44'}</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '35-44'}</t>
+          <t>35-44</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'55-64'}</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '55-64'}</t>
+          <t>55-64</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'65+'}</t>
+          <t>65+</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '65+'}</t>
+          <t>65+</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'semiannually'}</t>
+          <t>semiannually</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Semiannually'}</t>
+          <t>Semiannually</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'yearly'}</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Yearly'}</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'original'}</t>
+          <t>original</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Original'}</t>
+          <t>Original</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'mixed'}</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Mixed'}</t>
+          <t>Mixed</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'fruit_punch'}</t>
+          <t>fruit_punch</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Fruit Punch'}</t>
+          <t>Fruit Punch</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'berry'}</t>
+          <t>berry</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Berry'}</t>
+          <t>Berry</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
